--- a/outputs/excel-report-qa/review_results.xlsx
+++ b/outputs/excel-report-qa/review_results.xlsx
@@ -178,12 +178,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2类别1</t>
+          <t xml:space="preserve">2*类别1</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1类别2</t>
+          <t xml:space="preserve">1*类别2</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
@@ -210,7 +210,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1类别2+1类别3</t>
+          <t xml:space="preserve">1*类别2+1*类别3</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">

--- a/outputs/excel-report-qa/review_results.xlsx
+++ b/outputs/excel-report-qa/review_results.xlsx
@@ -128,7 +128,10 @@
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="34" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="23" customWidth="1"/>
+    <col min="7" max="7" width="23" customWidth="1"/>
+    <col min="8" max="8" width="23" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -161,7 +164,22 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">判定</t>
+          <t xml:space="preserve">人工判定模型结果</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">模型判定图片结果</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人工判定图片结果</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">模型判断是否正确</t>
         </is>
       </c>
     </row>
@@ -188,8 +206,22 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ng_漏检+误检</t>
-        </is>
+          <t xml:space="preserve">误检+漏检</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NG</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OK</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="str">
+        <f>IF(F3=G3,"正确","错误")</f>
+        <v>错误</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -215,8 +247,22 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ng_误检</t>
-        </is>
+          <t xml:space="preserve">误检</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OK</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OK</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="str">
+        <f>IF(F4=G4,"正确","错误")</f>
+        <v>正确</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -242,14 +288,28 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ok</t>
-        </is>
+          <t xml:space="preserve">无漏检无误检</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NG</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NG</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="str">
+        <f>IF(F5=G5,"正确","错误")</f>
+        <v>正确</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:E5"/>
+  <autoFilter ref="A2:H5"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
@@ -300,7 +360,7 @@
         </is>
       </c>
       <c r="B5" s="4">
-        <f>COUNTIF('图片明细'!E3:E5,"ng_*")</f>
+        <f>COUNTIF('图片明细'!E3:E5,"漏检")+COUNTIF('图片明细'!E3:E5,"误检")+COUNTIF('图片明细'!E3:E5,"误检+漏检")</f>
         <v>2</v>
       </c>
     </row>
@@ -311,7 +371,7 @@
         </is>
       </c>
       <c r="B6" s="4">
-        <f>COUNTIF('图片明细'!E3:E5,"ng_漏检")</f>
+        <f>COUNTIF('图片明细'!E3:E5,"漏检")</f>
         <v>0</v>
       </c>
     </row>
@@ -322,7 +382,7 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <f>COUNTIF('图片明细'!E3:E5,"ng_误检")</f>
+        <f>COUNTIF('图片明细'!E3:E5,"误检")</f>
         <v>1</v>
       </c>
     </row>
@@ -333,7 +393,7 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <f>COUNTIF('图片明细'!E3:E5,"ng_漏检+误检")</f>
+        <f>COUNTIF('图片明细'!E3:E5,"误检+漏检")</f>
         <v>1</v>
       </c>
     </row>
@@ -344,7 +404,7 @@
         </is>
       </c>
       <c r="B9" s="4">
-        <f>COUNTIF('图片明细'!E3:E5,"ok")</f>
+        <f>COUNTIF('图片明细'!E3:E5,"无漏检无误检")</f>
         <v>1</v>
       </c>
     </row>
